--- a/backend/wp_templates/D/D4-22至D4-32营业收入-IPO 上市 新三板 重组 舞弊应对.xlsx
+++ b/backend/wp_templates/D/D4-22至D4-32营业收入-IPO 上市 新三板 重组 舞弊应对.xlsx
@@ -24714,7 +24714,9 @@
       <c r="J17" s="122"/>
       <c r="K17" s="122"/>
       <c r="L17" s="122"/>
-      <c r="M17" s="122"/>
+      <c r="M17" s="122">
+        <f>SUM(C17:L17)</f>
+      </c>
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
       <c r="P17" s="133"/>
@@ -24736,7 +24738,9 @@
       <c r="J18" s="122"/>
       <c r="K18" s="122"/>
       <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
+      <c r="M18" s="122">
+        <f>SUM(C18:L18)</f>
+      </c>
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
       <c r="P18" s="133"/>
@@ -24758,7 +24762,9 @@
       <c r="J19" s="122"/>
       <c r="K19" s="122"/>
       <c r="L19" s="122"/>
-      <c r="M19" s="122"/>
+      <c r="M19" s="122">
+        <f>SUM(C19:L19)</f>
+      </c>
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
       <c r="P19" s="133"/>
